--- a/property_management_forms/043_property_rental_agreement_intake_form--property_management_forms.xlsx
+++ b/property_management_forms/043_property_rental_agreement_intake_form--property_management_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>month_to_month</t>
+          <t>month to month</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>month_to_month_with_option</t>
+          <t>month to month with option</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>year_to_year</t>
+          <t>year to year</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6_months</t>
+          <t>6 months</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12_months</t>
+          <t>12 months</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18_months</t>
+          <t>18 months</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>24_months</t>
+          <t>24 months</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>parking_available</t>
+          <t>parking available</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>extra_large</t>
+          <t>extra large</t>
         </is>
       </c>
     </row>
